--- a/stories/arbres/ATOM-TMP.MOI.001-04.xlsx
+++ b/stories/arbres/ATOM-TMP.MOI.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Yaël ouvre un calendrier avec maman. Maman lit les douze mois. Janvier, février, mars, avril. Mai, juin, juillet, août. Septembre, octobre, novembre, décembre. Yaël pose son doigt. Maman dit : en octobre, c'est ton anniversaire. Yaël sourit. Il y aura un gâteau. Papa arrivera avec des pommes. Maman répète : il y a douze mois. Un anniversaire a un mois. Plus tard, papa montre avril. Papa dit : mon anniversaire est en avril. Yaël dit : un anniversaire a un mois. Les douze mois sont là.</t>
+          <t>Yaël ouvre un calendrier avec maman. Maman lit les douze mois. Janvier, février, mars, avril. Mai, juin, juillet, août. Septembre, octobre, novembre, décembre. Yaël pose son doigt. En octobre, c'est ton anniversaire. Yaël sourit. Il y aura un gâteau. Papa arrivera avec des pommes. Maman répète : il y a douze mois. Un anniversaire a un mois. Plus tard, papa montre avril. Mon anniversaire est en avril. Un anniversaire a un mois. Les douze mois sont là.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Yaël ouvre un calendrier avec maman. Maman lit les douze mois. Janvier, février, mars, avril. Mai, juin, juillet, août. Septembre, octobre, novembre, décembre. Yaël pose son doigt.
+maman|En octobre, c'est ton anniversaire.
+narrateur|Yaël sourit. Il y aura un gâteau. Papa arrivera avec des pommes. Maman répète : il y a douze mois. Un anniversaire a un mois. Plus tard, papa montre avril.
+papa|Mon anniversaire est en avril.
+enfant-m|Un anniversaire a un mois.
+narrateur|Les douze mois sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1491,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Yaël a un gâteau en octobre. Pourquoi ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1664,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Yaël a entendu les douze mois. Son anniversaire est en octobre. Papa et maman étaient là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1827,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Yaël ferme le calendrier. Il range le crayon.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1994,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2034,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.MOI.001-04.xlsx
+++ b/stories/arbres/ATOM-TMP.MOI.001-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 narrateur|Les douze mois sont là.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1498,6 +1504,7 @@
           <t>narrateur|Yaël a un gâteau en octobre. Pourquoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1676,7 @@
           <t>narrateur|Yaël a entendu les douze mois. Son anniversaire est en octobre. Papa et maman étaient là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1832,6 +1840,7 @@
           <t>narrateur|Yaël ferme le calendrier. Il range le crayon.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1999,6 +2008,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2017,7 +2027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2051,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2242,6 +2266,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.MOI.001-04.xlsx
+++ b/stories/arbres/ATOM-TMP.MOI.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L'anniversaire de Yaël en octobre</t>
+          <t>La châtaigne trop fermée</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>C'est l'anniversaire de Raphaël, en octobre, quand les châtaignes tombent. Le vent pousse les feuilles. Une châtaigne est trop fermée. Ils en trouvent une ouverte, la font chauffer. Le gâteau attend.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Yaël ouvre un calendrier avec maman. Maman lit les douze mois. Janvier, février, mars, avril. Mai, juin, juillet, août. Septembre, octobre, novembre, décembre. Yaël pose son doigt. En octobre, c'est ton anniversaire. Yaël sourit. Il y aura un gâteau. Papa arrivera avec des pommes. Maman répète : il y a douze mois. Un anniversaire a un mois. Plus tard, papa montre avril. Mon anniversaire est en avril. Un anniversaire a un mois. Les douze mois sont là.</t>
+          <t>Le vent pousse les feuilles jusqu'au perron. Elles tapent le bois, sèches, brunes. Le châtaignier grince un peu. C'est mon jour. C'est octobre, Raphaël. Ton anniversaire. Les châtaignes tombent. On en cherche pour le goûter. Raphaël enfile ses gants rêches. Le cuir sent le grenier. Ils sont trop grands. Tu les gardes quand même. Une feuille se colle à sa manche. Elle me suit. Le vent la promène. Sous l'arbre, une bogue pique encore. Raphaël la retourne du bout du pied. Elle est fermée. Trop fermée. La châtaigne n'est pas sortie. Il cherche plus loin. Le vent lui jette trois feuilles au visage. Pff. Tu vois une ouverte ? En ce moment, une bogue fendue brille dans l'herbe. Deux châtaignes lisses y dorment. Celles-là. Elles sont prêtes. Papa les sort, tout doux. Elles sont froides, luisantes. Pour le gâteau ? À côté. On les chauffe.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Yaël ouvre un calendrier avec maman. Maman lit les &lt;emphasis level="moderate"&gt;douze&lt;/emphasis&gt; mois. Janvier, février, mars, avril. Mai, juin, juillet, août. Septembre, octobre, novembre, décembre. Yaël pose son doigt. Maman dit : en octobre, c'est ton anniversaire. Yaël sourit. Il y aura un gâteau. Papa arrivera avec des pommes. Maman répète : il y a douze mois. Un anniversaire a un mois. Plus tard, papa montre avril. Papa dit : mon anniversaire est en avril. Yaël dit : un anniversaire a un mois. Les douze mois sont là.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le vent pousse les feuilles jusqu'au perron. Elles tapent le bois, sèches, brunes. Le châtaignier grince un peu. C'est mon jour. C'est octobre, Raphaël. Ton anniversaire. Les châtaignes tombent. On en cherche pour le goûter. Raphaël enfile ses gants rêches. Le cuir sent le grenier. Ils sont trop grands. Tu les gardes quand même. Une feuille se colle à sa manche. Elle me suit. Le vent la promène. Sous l'arbre, une bogue pique encore. Raphaël la retourne du bout du pied. Elle est fermée. Trop fermée. La châtaigne n'est pas sortie. Il cherche plus loin. Le vent lui jette trois feuilles au visage. Pff. Tu vois une ouverte ? En ce moment, une bogue fendue brille dans l'herbe. Deux châtaignes lisses y dorment. Celles-là. Elles sont prêtes. Papa les sort, tout doux. Elles sont froides, luisantes. Pour le gâteau ? À côté. On les chauffe.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,15 +1324,41 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Yaël ouvre un calendrier avec maman. Maman lit les douze mois. Janvier, février, mars, avril. Mai, juin, juillet, août. Septembre, octobre, novembre, décembre. Yaël pose son doigt.
-maman|En octobre, c'est ton anniversaire.
-narrateur|Yaël sourit. Il y aura un gâteau. Papa arrivera avec des pommes. Maman répète : il y a douze mois. Un anniversaire a un mois. Plus tard, papa montre avril.
-papa|Mon anniversaire est en avril.
-enfant-m|Un anniversaire a un mois.
-narrateur|Les douze mois sont là.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le vent pousse les feuilles jusqu'au perron.
+narrateur|Elles tapent le bois, sèches, brunes.
+narrateur|Le châtaignier grince un peu.
+enfant-m|C'est mon jour.
+maman|C'est octobre, Raphaël.
+maman|Ton anniversaire.
+papa|Les châtaignes tombent.
+papa|On en cherche pour le goûter.
+narrateur|Raphaël enfile ses gants rêches.
+narrateur|Le cuir sent le grenier.
+enfant-m|Ils sont trop grands.
+papa|Tu les gardes quand même.
+narrateur|Une feuille se colle à sa manche.
+enfant-m|Elle me suit.
+maman|Le vent la promène.
+narrateur|Sous l'arbre, une bogue pique encore.
+narrateur|Raphaël la retourne du bout du pied.
+enfant-m|Elle est fermée.
+papa|Trop fermée.
+papa|La châtaigne n'est pas sortie.
+narrateur|Il cherche plus loin.
+narrateur|Le vent lui jette trois feuilles au visage.
+enfant-m|Pff.
+maman|Tu vois une ouverte ?
+narrateur|En ce moment, une bogue fendue brille dans l'herbe.
+narrateur|Deux châtaignes lisses y dorment.
+enfant-m|Celles-là.
+maman|Elles sont prêtes.
+narrateur|Papa les sort, tout doux.
+narrateur|Elles sont froides, luisantes.
+enfant-m|Pour le gâteau ?
+papa|À côté.
+papa|On les chauffe.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1345,19 +1383,19 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>Raphaël a un gâteau en octobre. Pourquoi ?</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Raphaël a un gâteau en octobre. Pourquoi ?</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>Yaël a un gâteau en octobre. Pourquoi ?</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Yaël a un gâteau en octobre. Pourquoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Yaël a un gâteau en octobre. Pourquoi ?</t>
-        </is>
-      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>anniversaire</t>
@@ -1365,7 +1403,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>anniversaire | son anniversaire | octobre | le mois</t>
+          <t>anniversaire | son anniversaire | octobre | le mois | châtaignes</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1422,14 +1460,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1501,10 +1539,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Yaël a un gâteau en octobre. Pourquoi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Raphaël a un gâteau en octobre.
+narrateur|Pourquoi ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1529,12 +1567,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Yaël a entendu les douze mois. Son anniversaire est en octobre. Papa et maman étaient là.</t>
+          <t>La cuisine sent déjà la pâte aux noisettes. Le gâteau d'octobre attend sur la grille. C'est ton anniversaire. En octobre. Oui. Papa pose les châtaignes dans la poêle. Il les fend d'un cran, tout petit. Pour qu'elles n'explosent pas. Oui. Ça crépite. Une peau se fend, chaude. Tu souffles un peu. Raphaël souffle. La vapeur lui chatouille le nez. Ça sent le bois. C'est octobre. Merci, Raphaël. Tu as trouvé les ouvertes. Pas la fermée. La fermée restera sous l'arbre.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Yaël a entendu les &lt;emphasis level="moderate"&gt;douze&lt;/emphasis&gt; mois. Son anniversaire est en octobre. Papa et maman étaient là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La cuisine sent déjà la pâte aux noisettes. Le gâteau d'octobre attend sur la grille. C'est ton anniversaire. En octobre. Oui. Papa pose les châtaignes dans la poêle. Il les fend d'un cran, tout petit. Pour qu'elles n'explosent pas. Oui. Ça crépite. Une peau se fend, chaude. Tu souffles un peu. Raphaël souffle. La vapeur lui chatouille le nez. Ça sent le bois. C'est octobre. Merci, Raphaël. Tu as trouvé les ouvertes. Pas la fermée. La fermée restera sous l'arbre.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1597,7 +1635,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1673,10 +1711,28 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Yaël a entendu les douze mois. Son anniversaire est en octobre. Papa et maman étaient là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|La cuisine sent déjà la pâte aux noisettes.
+narrateur|Le gâteau d'octobre attend sur la grille.
+maman|C'est ton anniversaire.
+enfant-m|En octobre.
+papa|Oui.
+narrateur|Papa pose les châtaignes dans la poêle.
+narrateur|Il les fend d'un cran, tout petit.
+enfant-m|Pour qu'elles n'explosent pas.
+papa|Oui.
+narrateur|Ça crépite.
+narrateur|Une peau se fend, chaude.
+maman|Tu souffles un peu.
+narrateur|Raphaël souffle.
+narrateur|La vapeur lui chatouille le nez.
+enfant-m|Ça sent le bois.
+maman|C'est octobre.
+papa|Merci, Raphaël.
+papa|Tu as trouvé les ouvertes.
+enfant-m|Pas la fermée.
+maman|La fermée restera sous l'arbre.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1701,12 +1757,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Yaël ferme le calendrier. Il range le crayon.</t>
+          <t>Maman pose une châtaigne chaude près du gâteau. L'autre reste dans la petite coupelle. Je pèle. La peau craque. Le dedans est jaune, tout doux. Tu goûtes ? Elle brûle un peu. On attend. Le vent frappe encore la vitre. Une feuille reste collée, comme une étoile. Elle veut entrer. Elle reste dehors. Raphaël souffle encore sur la châtaigne. Il la mange, enfin. Et le gâteau ? Après. C'est ton jour. Une miette de peau tombe sur la table.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Yaël ferme le calendrier. Il range le crayon.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman pose une châtaigne chaude près du gâteau. L'autre reste dans la petite coupelle. Je pèle. La peau craque. Le dedans est jaune, tout doux. Tu goûtes ? Elle brûle un peu. On attend. Le vent frappe encore la vitre. Une feuille reste collée, comme une étoile. Elle veut entrer. Elle reste dehors. Raphaël souffle encore sur la châtaigne. Il la mange, enfin. Et le gâteau ? Après. C'est ton jour. Une miette de peau tombe sur la table.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1769,7 +1825,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1837,10 +1893,26 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Yaël ferme le calendrier. Il range le crayon.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Maman pose une châtaigne chaude près du gâteau.
+narrateur|L'autre reste dans la petite coupelle.
+enfant-m|Je pèle.
+narrateur|La peau craque.
+narrateur|Le dedans est jaune, tout doux.
+papa|Tu goûtes ?
+enfant-m|Elle brûle un peu.
+maman|On attend.
+narrateur|Le vent frappe encore la vitre.
+narrateur|Une feuille reste collée, comme une étoile.
+enfant-m|Elle veut entrer.
+papa|Elle reste dehors.
+narrateur|Raphaël souffle encore sur la châtaigne.
+narrateur|Il la mange, enfin.
+maman|Et le gâteau ?
+enfant-m|Après.
+papa|C'est ton jour.
+narrateur|Une miette de peau tombe sur la table.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1865,12 +1937,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La poêle se tait. Il reste une odeur de bois chaud. Octobre est bon. C'est ton mois. Celui de ton anniversaire. Raphaël pose le gant près de la porte. Une feuille sèche y reste coincée. Elle m'a suivi. Tu peux la garder. Le gâteau attend encore une part. Dehors, la bogue fermée dort sous le vent.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La poêle se tait. Il reste une odeur de bois chaud. Octobre est bon. C'est ton mois. Celui de ton anniversaire. Raphaël pose le gant près de la porte. Une feuille sèche y reste coincée. Elle m'a suivi. Tu peux la garder. Le gâteau attend encore une part. Dehors, la bogue fermée dort sous le vent.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1933,7 +2005,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2005,10 +2077,19 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|La poêle se tait.
+narrateur|Il reste une odeur de bois chaud.
+enfant-m|Octobre est bon.
+maman|C'est ton mois.
+papa|Celui de ton anniversaire.
+narrateur|Raphaël pose le gant près de la porte.
+narrateur|Une feuille sèche y reste coincée.
+enfant-m|Elle m'a suivi.
+maman|Tu peux la garder.
+narrateur|Le gâteau attend encore une part.
+narrateur|Dehors, la bogue fermée dort sous le vent.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2027,7 +2108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2065,6 +2146,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.MOI.001-04.xlsx
+++ b/stories/arbres/ATOM-TMP.MOI.001-04.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>maison</t>
+          <t>allée sous le châtaignier, puis cuisine venteuse</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Yaël, maman, papa</t>
+          <t>Raphaël, maman, papa</t>
         </is>
       </c>
     </row>
